--- a/customer_registration_forms/009_plan_document_checklist--customer_registration_forms.xlsx
+++ b/customer_registration_forms/009_plan_document_checklist--customer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>created_by_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>Created By 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>updated_by_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Updated By</t>
+          <t>Updated By 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>updated_time</t>
+          <t>updated_time_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Updated Time</t>
+          <t>Updated Time 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>deleted_at_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Deleted At</t>
+          <t>Deleted At 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'name1',_'value':_'name1'}</t>
+          <t>name1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'name1', 'value': 'name1'}</t>
+          <t>name1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'name2',_'value':_'name2'}</t>
+          <t>name2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'name2', 'value': 'name2'}</t>
+          <t>name2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'name3',_'value':_'name3'}</t>
+          <t>name3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'name3', 'value': 'name3'}</t>
+          <t>name3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'duration1',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'duration1', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'duration2',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'duration2', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'duration3',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'duration3', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'status1',_'value':_'status1'}</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'status1', 'value': 'status1'}</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'status2',_'value':_'status2'}</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'status2', 'value': 'status2'}</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'status3',_'value':_'status3'}</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'status3', 'value': 'status3'}</t>
+          <t>Status 3</t>
         </is>
       </c>
     </row>
